--- a/Result/profitability/3008.xlsx
+++ b/Result/profitability/3008.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>4.64</v>
       </c>
       <c r="M2" t="n">
-        <v>40.66999999999999</v>
+        <v>38.92375000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>52.0475</v>
+        <v>51.91625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>5.55</v>
       </c>
       <c r="M3" t="n">
-        <v>35.155</v>
+        <v>31.49125</v>
       </c>
       <c r="N3" t="n">
-        <v>52.48</v>
+        <v>51.2725</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>8.710000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>28.1175</v>
+        <v>26.545</v>
       </c>
       <c r="N4" t="n">
-        <v>51.91</v>
+        <v>51.25875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>6.17</v>
       </c>
       <c r="M5" t="n">
-        <v>22.85375</v>
+        <v>26.35</v>
       </c>
       <c r="N5" t="n">
-        <v>51.535</v>
+        <v>51.00875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>3.41</v>
       </c>
       <c r="M6" t="n">
-        <v>22.31375</v>
+        <v>20.145</v>
       </c>
       <c r="N6" t="n">
-        <v>50.24125</v>
+        <v>50.5125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>3.14</v>
       </c>
       <c r="M7" t="n">
-        <v>16.075</v>
+        <v>14.24375</v>
       </c>
       <c r="N7" t="n">
-        <v>50.035</v>
+        <v>50.21625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>5.5</v>
       </c>
       <c r="M8" t="n">
-        <v>10.46875</v>
+        <v>9.102500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>49.25125</v>
+        <v>49.2525</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13665</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6912</v>
+      </c>
+      <c r="E75" t="n">
+        <v>6753</v>
+      </c>
+      <c r="F75" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5148</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>37.67%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>951</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6099</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4670</v>
+      </c>
+      <c r="L75" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="M75" t="n">
+        <v>44.55249999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>51.4825</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-10.93</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.234398455929659</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.01000000000000512</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.0002023881805304217</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.61836998706339</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.210000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07850083908260308</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
